--- a/data/04_scores.xlsx
+++ b/data/04_scores.xlsx
@@ -579,19 +579,19 @@
         </is>
       </c>
       <c r="E2" s="4" t="n">
-        <v>73.54468146258503</v>
+        <v>75.84258431972789</v>
       </c>
       <c r="F2" s="4" t="n">
         <v>100</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>83.26336827380953</v>
+        <v>84.11549384523809</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>72.15901771498478</v>
+        <v>73.19908724616558</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>69.99292637587098</v>
+        <v>72.09099757523673</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1</v>
@@ -629,19 +629,19 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>72.08297911564625</v>
+        <v>73.0359762585034</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>99.47087565339953</v>
+        <v>97.74266376981276</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>80.0517732142857</v>
+        <v>80.61983635714284</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>71.95795675865831</v>
+        <v>72.41281954276745</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>67.00778316834938</v>
+        <v>67.8551892267169</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>2</v>
@@ -679,19 +679,19 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>68.67280166666666</v>
+        <v>69.99237023809523</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>92.45537985203927</v>
+        <v>92.03088928678423</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>76.44417491666667</v>
+        <v>78.75341991666667</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>67.98539535664416</v>
+        <v>68.77484950670654</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>64.91847581566435</v>
+        <v>65.99964624820682</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>3</v>
@@ -715,48 +715,48 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>GHA</t>
+          <t>NAM</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>64.374865</v>
+        <v>65.83633547619047</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>76.23041703965362</v>
+        <v>73.61790402261423</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>70.10836524999999</v>
+        <v>71.04460208333333</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>64.9921000417169</v>
+        <v>65.31044583878277</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>63.3796170676524</v>
+        <v>64.84491776448081</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -779,25 +779,25 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>64.29778857142857</v>
+        <v>65.34480285714285</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>77.66645447203857</v>
+        <v>77.35071212668714</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>69.5130705</v>
+        <v>70.26521100000001</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>63.69427607745291</v>
+        <v>64.26999955204604</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>63.58783839521526</v>
+        <v>64.64490640149462</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>9</v>
@@ -806,7 +806,7 @@
         <v>7</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -815,42 +815,42 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>NAM</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>64.11924119047619</v>
+        <v>65.00660880952381</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>72.85018971581103</v>
+        <v>79.94511533609666</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>70.33368308333333</v>
+        <v>72.04973408333333</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>64.6833151367295</v>
+        <v>64.44405519522515</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>62.99565746786189</v>
+        <v>63.79191168079837</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>5</v>
@@ -879,31 +879,31 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>63.67873880952381</v>
+        <v>64.40698738095239</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>82.46846696273045</v>
+        <v>80.93119911051993</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>73.35686991666667</v>
+        <v>73.78934891666667</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>64.0921041982658</v>
+        <v>64.22801427125054</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>61.40166982608871</v>
+        <v>62.17133460119454</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>4</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N8" s="2" t="n">
         <v>8</v>
@@ -915,45 +915,45 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>GHA</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>62.90416023809524</v>
+        <v>64.06563357142858</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>78.64362885339744</v>
+        <v>73.33566548808017</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>69.84195208333335</v>
+        <v>70.00013425</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>63.50795078567664</v>
+        <v>64.43832361179476</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>61.82733452078001</v>
+        <v>62.91261892532123</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>7</v>
@@ -965,48 +965,48 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>STP</t>
+          <t>RWA</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Sao Tome &amp; Principe</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Islands</t>
+          <t>East</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>62.2043688095238</v>
+        <v>62.37999464285713</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>74.96211762548268</v>
+        <v>67.23226456628525</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>67.95617141666665</v>
+        <v>69.10780224999999</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>62.86564666544396</v>
+        <v>61.3406213413563</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>61.22996884289149</v>
+        <v>60.39299926875988</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -1015,48 +1015,48 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>RWA</t>
+          <t>STP</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Sao Tome &amp; Principe</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>Islands</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>61.5708175</v>
+        <v>61.87961738095237</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>67.07077757243574</v>
+        <v>72.00175561334285</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>68.731133625</v>
+        <v>67.84250841666666</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>60.87186485975464</v>
+        <v>62.18259964590714</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>59.58318015317174</v>
+        <v>60.79804648120669</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>EGY</t>
+          <t>TUN</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1079,34 +1079,34 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>59.74061035714284</v>
+        <v>61.06381059523809</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>82.35502735395053</v>
+        <v>78.91693913218631</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>71.021444375</v>
+        <v>71.87697720833334</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>58.63951010010614</v>
+        <v>60.23316297174569</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>50.31956713038499</v>
+        <v>56.72249088289738</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -1115,12 +1115,12 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>DZA</t>
+          <t>EGY</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1129,34 +1129,34 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>59.08397297619047</v>
+        <v>60.81685892857141</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>81.37284515182779</v>
+        <v>81.83407404310921</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>69.46245204166667</v>
+        <v>71.41850712499999</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>57.55161370631291</v>
+        <v>59.1731139424646</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>45.56803239971505</v>
+        <v>51.15751354486226</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
@@ -1165,48 +1165,48 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>TUN</t>
+          <t>ZAF</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>58.87472773809523</v>
+        <v>60.71372571428572</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>77.33397998218592</v>
+        <v>76.03220741826655</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>68.91602520833334</v>
+        <v>66.51245299999999</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>59.15103144427025</v>
+        <v>60.27862457438654</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>54.91292991213549</v>
+        <v>59.06860651853641</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L14" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="M14" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="M14" s="2" t="n">
-        <v>12</v>
-      </c>
       <c r="N14" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -1215,48 +1215,48 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>ZAF</t>
+          <t>DZA</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>57.77584571428572</v>
+        <v>59.5017644047619</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>73.97688559117169</v>
+        <v>80.30423004406111</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>65.19664599999999</v>
+        <v>69.83739704166666</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>59.21009521104391</v>
+        <v>57.9860568385568</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>55.89864086736799</v>
+        <v>45.8421182202415</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -1265,48 +1265,48 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>GMB</t>
+          <t>KEN</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>The Gambia</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>57.38200261904761</v>
+        <v>57.04817488095238</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>63.33540421040031</v>
+        <v>59.59180448469892</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>62.19883258333333</v>
+        <v>62.73077133333332</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>56.11878444391812</v>
+        <v>55.22851007300346</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>56.51813084193746</v>
+        <v>55.87862609006943</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>GMB</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>The Gambia</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1329,19 +1329,19 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>56.36888166666667</v>
+        <v>56.69232547619048</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>62.29956347502075</v>
+        <v>61.48774388619471</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>63.69375266666666</v>
+        <v>61.95744558333332</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>52.81742684495967</v>
+        <v>55.82777816063733</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>53.70928987179892</v>
+        <v>55.79237077100933</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>16</v>
@@ -1350,13 +1350,13 @@
         <v>16</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>CIV</t>
+          <t>BEN</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1379,34 +1379,34 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>56.18353035714286</v>
+        <v>56.00220166666666</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>57.68358767083696</v>
+        <v>61.58686441399743</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>62.813854625</v>
+        <v>62.96749866666666</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>54.15654424681628</v>
+        <v>53.06675178601531</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>54.84134066260032</v>
+        <v>53.43571647434554</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="K18" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="M18" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="L18" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>18</v>
-      </c>
       <c r="N18" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -1415,48 +1415,48 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>KEN</t>
+          <t>CIV</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Cote d'Ivoire</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>56.03501773809524</v>
+        <v>55.88096464285714</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>58.34423395713804</v>
+        <v>57.65942682310715</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>60.99157433333333</v>
+        <v>62.263220625</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>54.61024892651054</v>
+        <v>54.41556911948647</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>54.96528866335748</v>
+        <v>54.60696121434528</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1479,19 +1479,19 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>55.83531857142857</v>
+        <v>55.31639000000001</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>54.35162389621673</v>
+        <v>53.49227318419977</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>65.01712291666666</v>
+        <v>64.97503391666667</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>54.71279290775113</v>
+        <v>54.48419795655956</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>51.92597426988822</v>
+        <v>51.39270591919193</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>19</v>
@@ -1503,10 +1503,10 @@
         <v>16</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>ZMB</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1529,34 +1529,34 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>54.28169666666665</v>
+        <v>53.91583083333333</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>55.52989535818064</v>
+        <v>50.52093775094176</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>62.08058716666667</v>
+        <v>62.53110329166667</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>53.76250411225683</v>
+        <v>52.947025980163</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>52.57715246955047</v>
+        <v>51.4511898245941</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>MWI</t>
+          <t>ZMB</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1579,34 +1579,34 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>54.0113875</v>
+        <v>53.53418238095237</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>53.57232155808028</v>
+        <v>53.91262482593147</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>65.34066375</v>
+        <v>61.81895716666666</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>53.56489787288933</v>
+        <v>53.35146514969473</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>50.20764942006542</v>
+        <v>51.72850223233017</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>MWI</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1629,34 +1629,34 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>53.83625369047618</v>
+        <v>52.98612464285715</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>50.15976546555689</v>
+        <v>51.23580980393447</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>62.51556829166665</v>
+        <v>64.98182174999999</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>52.77927414673729</v>
+        <v>52.78555901027934</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>51.32236929774869</v>
+        <v>48.82403832919749</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24">
@@ -1665,48 +1665,48 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>GAB</t>
+          <t>COM</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Islands</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>53.24272323129252</v>
+        <v>52.87222333333333</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>59.8876147839422</v>
+        <v>55.22267863158403</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>62.13246698809524</v>
+        <v>59.64954983333332</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>48.81486496204008</v>
+        <v>50.54903038698374</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>51.32575590181248</v>
+        <v>51.535039302648</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
@@ -1715,45 +1715,45 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>COM</t>
+          <t>TGO</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Islands</t>
+          <t>West</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>52.59313476190475</v>
+        <v>52.82376547619047</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>54.84724323373241</v>
+        <v>53.40963324502296</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>59.47427183333333</v>
+        <v>59.80890541666667</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>50.22454028411016</v>
+        <v>50.7944940020711</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>51.27006780431459</v>
+        <v>51.37188715604188</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>22</v>
@@ -1765,48 +1765,48 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>TGO</t>
+          <t>TZA</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>52.47196833333333</v>
+        <v>52.73023892857143</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>52.49980384867631</v>
+        <v>55.22740923028478</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>59.27360041666667</v>
+        <v>57.47364262500001</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>50.30687650625312</v>
+        <v>51.14723231856524</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>51.05746118372527</v>
+        <v>51.8691252256962</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
@@ -1815,48 +1815,48 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>TZA</t>
+          <t>SWZ</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>South</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>52.27106178571429</v>
+        <v>51.87443547619048</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>54.62987763652847</v>
+        <v>53.22059703283946</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>57.17262912500001</v>
+        <v>58.65666016666666</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>50.7341292801636</v>
+        <v>51.75245516599042</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>51.40863941545896</v>
+        <v>50.53211761031524</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="K27" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="N27" s="2" t="n">
         <v>24</v>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="M27" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N27" s="2" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="28">
@@ -1865,48 +1865,48 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>SWZ</t>
+          <t>DJI</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Djibouti</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>East</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>51.17817547619048</v>
+        <v>51.07651488095238</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>52.43623890067296</v>
+        <v>51.19258392876232</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>57.82528541666666</v>
+        <v>57.49108433333333</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>51.52952572191078</v>
+        <v>49.66102881686326</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>49.83411023978235</v>
+        <v>49.86930242497849</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
@@ -1915,48 +1915,48 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>DJI</t>
+          <t>GAB</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Djibouti</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>50.6430605952381</v>
+        <v>50.9512975170068</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>49.69856694820729</v>
+        <v>57.31154397995368</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>56.73253933333334</v>
+        <v>58.12247198809523</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>49.0275570030426</v>
+        <v>48.424619074866</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>49.50492165488383</v>
+        <v>49.72775148407416</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>28</v>
       </c>
       <c r="K29" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="L29" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="L29" s="2" t="n">
-        <v>33</v>
-      </c>
       <c r="M29" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>SLE</t>
+          <t>MRT</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Mauritania</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -1979,34 +1979,34 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>50.42526869047618</v>
+        <v>50.79295261904762</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>47.4533354499185</v>
+        <v>59.31509066724604</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>61.70816320833332</v>
+        <v>56.68501241666667</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>48.68969451933111</v>
+        <v>48.18716771365467</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>45.97199213006903</v>
+        <v>49.61901467901248</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>MRT</t>
+          <t>SLE</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Mauritania</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -2029,34 +2029,34 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>50.41801547619048</v>
+        <v>50.36749154761904</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>58.49694404353444</v>
+        <v>47.21458137348316</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>56.08912741666667</v>
+        <v>61.68794120833333</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>47.47732831314254</v>
+        <v>48.6053574040578</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>49.33428471660653</v>
+        <v>45.92030142764278</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32">
@@ -2079,19 +2079,19 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>49.07460387755102</v>
+        <v>49.31901816326531</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>46.07517778614413</v>
+        <v>46.80607671981198</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>58.16348678571428</v>
+        <v>58.30180678571429</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>47.20746864124363</v>
+        <v>47.48743323596246</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>46.49316287888188</v>
+        <v>46.7867628743596</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>31</v>
@@ -2129,25 +2129,25 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>47.71854404761905</v>
+        <v>47.75496404761904</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>39.68825173137852</v>
+        <v>41.16424874768005</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>57.56155758333333</v>
+        <v>57.51112858333332</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>46.53571638914832</v>
+        <v>46.90756507634691</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>44.4752123518082</v>
+        <v>44.53476390804787</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>32</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>31</v>
@@ -2156,7 +2156,7 @@
         <v>32</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34">
@@ -2165,45 +2165,45 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>LBR</t>
+          <t>BDI</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>46.63310607142857</v>
+        <v>47.2809955952381</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>43.38337134386322</v>
+        <v>41.00326396585039</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>55.109126625</v>
+        <v>58.27416695833334</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>44.11647502242757</v>
+        <v>45.23935041542643</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>43.35203339672411</v>
+        <v>43.41299160912062</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>33</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="N34" s="2" t="n">
         <v>38</v>
@@ -2215,48 +2215,48 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>BDI</t>
+          <t>BFA</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>46.34398988095238</v>
+        <v>47.22244083333333</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>38.80932095927347</v>
+        <v>46.80288112277429</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>57.70811495833333</v>
+        <v>53.40532495833333</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>44.58190299372851</v>
+        <v>45.65165233868665</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>42.32611667362896</v>
+        <v>46.20215854427626</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>34</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="L35" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="N35" s="2" t="n">
         <v>30</v>
-      </c>
-      <c r="M35" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="N35" s="2" t="n">
-        <v>42</v>
       </c>
     </row>
     <row r="36">
@@ -2279,19 +2279,19 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>46.26680761904762</v>
+        <v>46.19042190476191</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>45.10715441226952</v>
+        <v>45.87356499133517</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>52.85427091666667</v>
+        <v>52.58528791666666</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>43.74705275937415</v>
+        <v>44.12566509221992</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>44.90293495587128</v>
+        <v>44.90787500671381</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>35</v>
@@ -2300,10 +2300,10 @@
         <v>34</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="N36" s="2" t="n">
         <v>33</v>
@@ -2315,12 +2315,12 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>BFA</t>
+          <t>LBR</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -2329,34 +2329,34 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>46.03568369047618</v>
+        <v>45.91922035714285</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>44.28557083258789</v>
+        <v>43.17154642867177</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>51.84858795833334</v>
+        <v>53.75834662500001</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>44.67363874353486</v>
+        <v>44.09051733600607</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>45.06101996395603</v>
+        <v>42.78902991472316</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>36</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L37" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="M37" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="M37" s="2" t="n">
-        <v>34</v>
-      </c>
       <c r="N37" s="2" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38">
@@ -2365,45 +2365,45 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>CMR</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>East</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>45.7497175</v>
+        <v>45.9049125</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>42.41038094085916</v>
+        <v>41.24264817678334</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>54.637440625</v>
+        <v>54.219617875</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>43.29317120948943</v>
+        <v>44.64841689329368</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>43.57592198571429</v>
+        <v>43.57345584660489</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>36</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="N38" s="2" t="n">
         <v>36</v>
@@ -2415,48 +2415,48 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>MOZ</t>
+          <t>CMR</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>45.56273892857143</v>
+        <v>45.73723178571428</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>38.81888787607199</v>
+        <v>43.36293864781752</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>53.679503375</v>
+        <v>54.615590625</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>44.31302933724581</v>
+        <v>43.52545380111397</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>42.98242211989147</v>
+        <v>43.5656793985405</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="L39" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="N39" s="2" t="n">
         <v>37</v>
-      </c>
-      <c r="M39" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="N39" s="2" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="40">
@@ -2465,48 +2465,48 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>COG</t>
+          <t>LBY</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Republic of Congo</t>
+          <t>Libya</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>45.50075517006803</v>
+        <v>45.0289630952381</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>45.34065270745079</v>
+        <v>58.17182239143701</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>50.01307763095237</v>
+        <v>60.63027108333334</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>43.79837009013497</v>
+        <v>43.20802869033966</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>44.76982639288559</v>
+        <v>28.84173236705238</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>MOZ</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -2529,34 +2529,34 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>45.47212964285714</v>
+        <v>44.96462464285714</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>39.64508758996737</v>
+        <v>38.84100629773157</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>53.500302875</v>
+        <v>52.594747375</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>44.31376146121945</v>
+        <v>44.11601867361912</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>43.18693703596386</v>
+        <v>42.41164809753672</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>40</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>AGO</t>
+          <t>COG</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Republic of Congo</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -2579,34 +2579,34 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>44.82618935374149</v>
+        <v>44.7323037414966</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>40.35439990664523</v>
+        <v>44.95125093036147</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>49.82637494047618</v>
+        <v>48.59640763095238</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>44.76216584927368</v>
+        <v>43.72249511721021</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>43.54162332329068</v>
+        <v>44.1224060870236</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>45</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43">
@@ -2615,48 +2615,48 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>LBY</t>
+          <t>MLI</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Libya</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>44.82205738095238</v>
+        <v>44.69666</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>57.64367579144272</v>
+        <v>41.38613443754593</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>60.40137708333334</v>
+        <v>52.61406999999999</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>42.59964736780405</v>
+        <v>44.11927142155358</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>28.72989390354143</v>
+        <v>42.84328307293147</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>42</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44">
@@ -2665,45 +2665,45 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>MLI</t>
+          <t>AGO</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>43.99627142857142</v>
+        <v>44.07143506802721</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>39.11453736394209</v>
+        <v>39.93334373962944</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>51.38838999999999</v>
+        <v>49.12235179761905</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>43.65100901237088</v>
+        <v>44.46831769413969</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>42.33584108577031</v>
+        <v>42.74367208405257</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="N44" s="2" t="n">
         <v>41</v>
@@ -2729,31 +2729,31 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>43.82710380952381</v>
+        <v>43.32344380952381</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>43.47350362750446</v>
+        <v>42.48881461740865</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>51.44590633333333</v>
+        <v>51.26962533333334</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>42.84110722216933</v>
+        <v>42.33506872474686</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>42.20709876690628</v>
+        <v>41.50860754376662</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>44</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N45" s="2" t="n">
         <v>43</v>
@@ -2779,19 +2779,19 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>42.64302928571428</v>
+        <v>42.45408928571429</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>36.57248368743169</v>
+        <v>37.71549481562855</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>50.98198825</v>
+        <v>50.61011724999999</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>40.46112094151818</v>
+        <v>40.66090939548896</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>39.62021656933283</v>
+        <v>39.4793308760457</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>45</v>
@@ -2829,28 +2829,28 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>39.72230142857143</v>
+        <v>39.53979</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>39.24919444923173</v>
+        <v>40.53336473934239</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>44.76352825</v>
+        <v>44.39339325</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>37.45734324754471</v>
+        <v>37.93959251113724</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>38.76645235413352</v>
+        <v>38.66552777850245</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M47" s="2" t="n">
         <v>46</v>
@@ -2865,33 +2865,33 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>GNQ</t>
+          <t>ERI</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Equatorial Guinea</t>
+          <t>Eritrea</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>East</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>37.73431693877551</v>
+        <v>38.12237095238095</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>34.73909061100958</v>
+        <v>33.05982121649279</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>43.57372464285714</v>
+        <v>44.85755883333334</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>33.32801848609545</v>
+        <v>36.6863400371132</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>35.71385794695092</v>
+        <v>35.76844442108064</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>47</v>
@@ -2900,10 +2900,10 @@
         <v>47</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N48" s="2" t="n">
         <v>46</v>
@@ -2915,45 +2915,45 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>ERI</t>
+          <t>GNQ</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Eritrea</t>
+          <t>Equatorial Guinea</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>35.42566238095237</v>
+        <v>34.90422836734694</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>27.85975269367827</v>
+        <v>33.04728843028256</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>41.14889083333334</v>
+        <v>38.67815364285715</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>35.4003639360338</v>
+        <v>32.79242467083707</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>33.45662544763312</v>
+        <v>34.06566702474874</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>48</v>
       </c>
       <c r="K49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="M49" s="2" t="n">
         <v>49</v>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="M49" s="2" t="n">
-        <v>48</v>
       </c>
       <c r="N49" s="2" t="n">
         <v>47</v>
@@ -2979,31 +2979,31 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>34.73979297619048</v>
+        <v>34.7829844047619</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>28.50957469743979</v>
+        <v>29.21768338038756</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>44.42566704166667</v>
+        <v>44.44078404166667</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>35.82228842513491</v>
+        <v>35.4891721200207</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>31.28734625863787</v>
+        <v>31.35411705566887</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>49</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>48</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N50" s="2" t="n">
         <v>48</v>
@@ -3029,25 +3029,25 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>33.37069724489795</v>
+        <v>33.5453943877551</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>17.74794662999058</v>
+        <v>21.07041981029052</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>45.77915917857144</v>
+        <v>46.06796717857144</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>30.51763953339073</v>
+        <v>31.16908625090716</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>27.24194337326238</v>
+        <v>27.35456075187597</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>50</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>46</v>
@@ -3079,28 +3079,28 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>30.67044469387755</v>
+        <v>30.53244469387755</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>17.84131893032054</v>
+        <v>20.65139152879808</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>39.46861814285715</v>
+        <v>39.16791814285715</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>28.38859528438223</v>
+        <v>28.92401225255659</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>27.03197553342536</v>
+        <v>26.99910340402668</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>51</v>
       </c>
       <c r="K52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="L52" s="2" t="n">
         <v>50</v>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>52</v>
       </c>
       <c r="M52" s="2" t="n">
         <v>51</v>
@@ -3115,48 +3115,48 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Central African Republic</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>East</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>28.39216952380952</v>
+        <v>27.47928130952381</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>10.0611005247444</v>
+        <v>18.65573584576429</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>39.76691316666667</v>
+        <v>36.21085795833333</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>26.27904073831306</v>
+        <v>25.45082178734095</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>21.60739747366392</v>
+        <v>23.42069549124077</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>52</v>
       </c>
       <c r="K53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="L53" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="L53" s="2" t="n">
-        <v>51</v>
-      </c>
       <c r="M53" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="N53" s="2" t="n">
         <v>52</v>
-      </c>
-      <c r="N53" s="2" t="n">
-        <v>53</v>
       </c>
     </row>
     <row r="54">
@@ -3165,48 +3165,48 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Central African Republic</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>28.1980155952381</v>
+        <v>27.23027523809523</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>17.43648818812443</v>
+        <v>11.85489620364568</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>37.56971895833333</v>
+        <v>37.70822616666667</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>25.53191061143373</v>
+        <v>26.24156921452244</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>23.96166390157579</v>
+        <v>21.04229484230262</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>53</v>
       </c>
       <c r="K54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="L54" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="L54" s="2" t="n">
+      <c r="M54" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="N54" s="2" t="n">
         <v>53</v>
-      </c>
-      <c r="M54" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="N54" s="2" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="55">
@@ -3229,19 +3229,19 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>20.33889261904762</v>
+        <v>17.76669261904761</v>
       </c>
       <c r="F55" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>29.55432291666666</v>
+        <v>25.05297291666666</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>18.9669423034948</v>
+        <v>18.12094695592511</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>13.19835386214734</v>
+        <v>11.88252299194859</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>54</v>
@@ -3537,10 +3537,10 @@
         <v>2</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>70.03700000000001</v>
+        <v>86.12232</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>85.16512857142857</v>
@@ -3596,7 +3596,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>72.5462</v>
+        <v>79.21718</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>3</v>
@@ -3655,7 +3655,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>75.33637999999999</v>
+        <v>84.61564</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>2</v>
@@ -3685,7 +3685,7 @@
         <v>49</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>78.8806</v>
+        <v>78.83832000000001</v>
       </c>
       <c r="Q4" s="2" t="n">
         <v>5</v>
@@ -3694,60 +3694,60 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GHA</t>
+          <t>NAM</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>70.64710000000001</v>
+        <v>80.12819999999999</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>46.22184</v>
+        <v>64.99138000000001</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>71.02164999999999</v>
+        <v>62.8114</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>50.86268</v>
+        <v>44.14032</v>
       </c>
       <c r="K5" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>65.20243333333333</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>77.523775</v>
+      </c>
+      <c r="O5" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="L5" s="4" t="n">
-        <v>79.326475</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>67.56235</v>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>25</v>
-      </c>
       <c r="P5" s="4" t="n">
-        <v>64.98196</v>
+        <v>66.05683999999999</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -3773,10 +3773,10 @@
         <v>9</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>59.5746</v>
+        <v>65.06438</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>64.70795</v>
@@ -3803,69 +3803,69 @@
         <v>37</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>66.55365999999999</v>
+        <v>68.39297999999999</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>NAM</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>80.12819999999999</v>
+        <v>59.39736666666667</v>
       </c>
       <c r="E7" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>74.83894000000001</v>
+      </c>
+      <c r="G7" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>53.52139999999999</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>28</v>
-      </c>
       <c r="H7" s="4" t="n">
-        <v>62.8114</v>
+        <v>73.24055</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>44.14032</v>
+        <v>80.92466</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>65.20243333333333</v>
+        <v>50.61907500000001</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>77.523775</v>
+        <v>46.09385</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>65.50716</v>
+        <v>69.93181999999999</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -3891,10 +3891,10 @@
         <v>4</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>53.25606000000001</v>
+        <v>57.46584</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>66.45779999999999</v>
@@ -3921,7 +3921,7 @@
         <v>43</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>79.40974000000001</v>
+        <v>80.29770000000001</v>
       </c>
       <c r="Q8" s="2" t="n">
         <v>4</v>
@@ -3930,189 +3930,189 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>GHA</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>59.39736666666667</v>
+        <v>70.64710000000001</v>
       </c>
       <c r="E9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>43.54982</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>71.02164999999999</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>50.86268</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>79.326475</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>67.56235</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="P9" s="4" t="n">
+        <v>65.48936</v>
+      </c>
+      <c r="Q9" s="2" t="n">
         <v>13</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>60.12180000000001</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>73.24055</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>80.92466</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>50.61907500000001</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v>46.09385</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v>69.93181999999999</v>
-      </c>
-      <c r="Q9" s="2" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>STP</t>
+          <t>RWA</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sao Tome &amp; Principe</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Islands</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>64.89803333333333</v>
+        <v>76.749</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>42.95318</v>
+        <v>61.246</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>79.38761666666666</v>
+        <v>62.4065625</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>62.95477999999999</v>
+        <v>33.23192</v>
       </c>
       <c r="K10" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>59.00310000000001</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>81.5646</v>
+      </c>
+      <c r="O10" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="L10" s="4" t="n">
-        <v>70.89886666666666</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v>58.459525</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>32</v>
-      </c>
       <c r="P10" s="4" t="n">
-        <v>55.87858</v>
+        <v>62.45877999999999</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>RWA</t>
+          <t>STP</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Sao Tome &amp; Principe</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>Islands</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>76.749</v>
+        <v>64.89803333333333</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>57.29423999999999</v>
+        <v>41.44101999999999</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>62.4065625</v>
+        <v>79.38761666666666</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>33.23192</v>
+        <v>62.95477999999999</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>59.00310000000001</v>
+        <v>70.89886666666666</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>81.5646</v>
+        <v>58.459525</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>60.7463</v>
+        <v>55.11748</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>EGY</t>
+          <t>TUN</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -4121,57 +4121,57 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>45.69045</v>
+        <v>58.82236666666666</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>61.47220000000001</v>
+        <v>75.46988</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>75.3911875</v>
+        <v>74.1327375</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>77.53673999999999</v>
+        <v>86.43412000000001</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>68.59842499999999</v>
+        <v>43.476725</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>9.011650000000001</v>
+        <v>23.164925</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>80.48362</v>
+        <v>65.94592</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>DZA</t>
+          <t>EGY</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -4180,234 +4180,234 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>47.84208333333333</v>
+        <v>45.69045</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>68.21640000000001</v>
+        <v>69.00594</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>8</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>72.7669875</v>
+        <v>75.3911875</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>83.50322000000001</v>
+        <v>77.53673999999999</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>70.59099999999999</v>
+        <v>68.59842499999999</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>4.397600000000001</v>
+        <v>9.011650000000001</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>66.27052</v>
+        <v>80.48362</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>TUN</t>
+          <t>ZAF</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>58.82236666666666</v>
+        <v>69.69165</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>60.1463</v>
+        <v>63.48445999999999</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>74.1327375</v>
+        <v>63.6929</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>86.43412000000001</v>
+        <v>59.84764</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>43.476725</v>
+        <v>57.84785</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>23.164925</v>
+        <v>33.374</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>65.94592</v>
+        <v>77.05758</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>ZAF</t>
+          <t>DZA</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>69.69165</v>
+        <v>47.84208333333333</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>43.44784</v>
+        <v>71.14093999999999</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>63.6929</v>
+        <v>72.7669875</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>59.84764</v>
+        <v>83.50322000000001</v>
       </c>
       <c r="K15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>70.59099999999999</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>4.397600000000001</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="P15" s="4" t="n">
+        <v>66.27052</v>
+      </c>
+      <c r="Q15" s="2" t="n">
         <v>10</v>
-      </c>
-      <c r="L15" s="4" t="n">
-        <v>57.84785</v>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="N15" s="4" t="n">
-        <v>33.374</v>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="P15" s="4" t="n">
-        <v>76.52904000000001</v>
-      </c>
-      <c r="Q15" s="2" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>GMB</t>
+          <t>KEN</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>The Gambia</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>61.43373333333333</v>
+        <v>54.86836666666667</v>
       </c>
       <c r="E16" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>65.34175999999999</v>
+      </c>
+      <c r="G16" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F16" s="4" t="n">
-        <v>55.87760000000001</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>23</v>
-      </c>
       <c r="H16" s="4" t="n">
-        <v>60.65519999999999</v>
+        <v>57.7488625</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>38.47714</v>
+        <v>37.01766</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>68.1091</v>
+        <v>58.022975</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>65.86902499999999</v>
+        <v>76.0176</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>51.25222</v>
+        <v>50.31999999999999</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>GMB</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>The Gambia</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -4416,57 +4416,57 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>62.91281666666666</v>
+        <v>61.43373333333333</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>68.64986</v>
+        <v>50.60590000000001</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>58.16215</v>
+        <v>60.65519999999999</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>24.91164</v>
+        <v>38.47714</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>73.68334999999999</v>
+        <v>68.1091</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>58.308775</v>
+        <v>65.86902499999999</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>47.95358</v>
+        <v>51.69618000000001</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>CIV</t>
+          <t>BEN</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -4475,105 +4475,105 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>55.9895</v>
+        <v>62.91281666666666</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>70.52302</v>
+        <v>65.66028000000001</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>49.9701875</v>
+        <v>58.16215</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>36.87752</v>
+        <v>24.91164</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>52.5138</v>
+        <v>73.68334999999999</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>76.107125</v>
+        <v>58.308775</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>51.30355999999999</v>
+        <v>48.3764</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>KEN</t>
+          <t>CIV</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Cote d'Ivoire</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>54.86836666666667</v>
+        <v>55.9895</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>58.4188</v>
+        <v>68.29934</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>57.7488625</v>
+        <v>49.9701875</v>
       </c>
       <c r="I19" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>36.87752</v>
+      </c>
+      <c r="K19" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="J19" s="4" t="n">
-        <v>37.01766</v>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>24</v>
-      </c>
       <c r="L19" s="4" t="n">
-        <v>58.022975</v>
+        <v>52.5138</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>76.0176</v>
+        <v>76.107125</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>50.15086</v>
+        <v>51.40928</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
@@ -4599,10 +4599,10 @@
         <v>15</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>53.99038</v>
+        <v>49.6602</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="H20" s="4" t="n">
         <v>56.022475</v>
@@ -4629,21 +4629,21 @@
         <v>1</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>61.16518000000001</v>
+        <v>61.86286</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>ZMB</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -4652,57 +4652,57 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>57.89811666666666</v>
+        <v>46.35143333333334</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>48.53622</v>
+        <v>52.78220000000001</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>53.0586</v>
+        <v>55.9840375</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>34.02714</v>
+        <v>36.58566</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>68.262</v>
+        <v>55.775725</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>75.98520000000001</v>
+        <v>93.3475</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>42.2046</v>
+        <v>36.58426</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>MWI</t>
+          <t>ZMB</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -4711,57 +4711,57 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>57.5232</v>
+        <v>57.89811666666666</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>40.39444</v>
+        <v>42.77508</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>54.7145625</v>
+        <v>53.0586</v>
       </c>
       <c r="I22" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>34.02714</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>68.262</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>75.98520000000001</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="P22" s="4" t="n">
+        <v>42.73314</v>
+      </c>
+      <c r="Q22" s="2" t="n">
         <v>29</v>
-      </c>
-      <c r="J22" s="4" t="n">
-        <v>24.41694</v>
-      </c>
-      <c r="K22" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v>77.36920000000001</v>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N22" s="4" t="n">
-        <v>83.61235000000001</v>
-      </c>
-      <c r="O22" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="P22" s="4" t="n">
-        <v>40.04902000000001</v>
-      </c>
-      <c r="Q22" s="2" t="n">
-        <v>34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>MWI</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -4770,411 +4770,411 @@
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>46.35143333333334</v>
+        <v>57.5232</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>53.02854</v>
+        <v>33.2176</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>55.9840375</v>
+        <v>54.7145625</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>36.58566</v>
+        <v>24.41694</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>55.775725</v>
+        <v>77.36920000000001</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>93.3475</v>
+        <v>83.61235000000001</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>35.78088</v>
+        <v>40.04902000000001</v>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>GAB</t>
+          <t>COM</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Islands</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>44.50793333333333</v>
+        <v>35.06</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>80.73594</v>
+        <v>57.54389999999999</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>62.03461428571428</v>
+        <v>63.01073333333333</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>38.78836</v>
+        <v>40.02670000000001</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>36.688675</v>
+        <v>62.00539999999999</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>46.9687</v>
+        <v>66.31925</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>62.97484000000001</v>
+        <v>46.13958</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>COM</t>
+          <t>TGO</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Islands</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>35.06</v>
+        <v>48.13568333333333</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>55.99195999999999</v>
+        <v>62.92229999999999</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>63.01073333333333</v>
+        <v>52.98165</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>40.02670000000001</v>
+        <v>33.56918</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>62.00539999999999</v>
+        <v>57.996275</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>66.31925</v>
+        <v>72.43895000000001</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>45.7379</v>
+        <v>41.72232</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TGO</t>
+          <t>TZA</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>48.13568333333333</v>
+        <v>56.48875</v>
       </c>
       <c r="E26" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>56.64162</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>58.9782125</v>
+      </c>
+      <c r="I26" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="F26" s="4" t="n">
-        <v>60.86142</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>52.98165</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>32</v>
-      </c>
       <c r="J26" s="4" t="n">
-        <v>33.56918</v>
+        <v>36.31216000000001</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>57.996275</v>
+        <v>51.77327500000001</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>72.43895000000001</v>
+        <v>65.348275</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>41.32062000000001</v>
+        <v>43.56938</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>TZA</t>
+          <t>SWZ</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>56.48875</v>
+        <v>45.62751666666667</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>54.2942</v>
+        <v>50.39726</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>58.9782125</v>
+        <v>48.717075</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>36.31216000000001</v>
+        <v>37.39032</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>51.77327500000001</v>
+        <v>41.06236666666667</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>65.348275</v>
+        <v>71.75725</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>42.70256</v>
+        <v>68.16926000000001</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>SWZ</t>
+          <t>DJI</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Djibouti</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>45.62751666666667</v>
+        <v>43.79846666666666</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>46.13654</v>
+        <v>65.52849999999999</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>48.717075</v>
+        <v>47.2525625</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>37.39032</v>
+        <v>39.08702</v>
       </c>
       <c r="K28" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>41.139175</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="N28" s="4" t="n">
+        <v>71.61020000000001</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="P28" s="4" t="n">
+        <v>49.11968</v>
+      </c>
+      <c r="Q28" s="2" t="n">
         <v>23</v>
-      </c>
-      <c r="L28" s="4" t="n">
-        <v>41.06236666666667</v>
-      </c>
-      <c r="M28" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="N28" s="4" t="n">
-        <v>71.75725</v>
-      </c>
-      <c r="O28" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="P28" s="4" t="n">
-        <v>67.55616000000001</v>
-      </c>
-      <c r="Q28" s="2" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>DJI</t>
+          <t>GAB</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Djibouti</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>43.79846666666666</v>
+        <v>44.50793333333333</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>63.34</v>
+        <v>64.48454000000001</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>47.2525625</v>
+        <v>62.03461428571428</v>
       </c>
       <c r="I29" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>38.78836</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>36.688675</v>
+      </c>
+      <c r="M29" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="J29" s="4" t="n">
-        <v>39.08702</v>
-      </c>
-      <c r="K29" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="L29" s="4" t="n">
-        <v>41.139175</v>
-      </c>
-      <c r="M29" s="2" t="n">
-        <v>37</v>
-      </c>
       <c r="N29" s="4" t="n">
-        <v>71.61020000000001</v>
+        <v>46.9687</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>48.274</v>
+        <v>63.18626</v>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>SLE</t>
+          <t>MRT</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Mauritania</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -5183,57 +5183,57 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>47.22963333333333</v>
+        <v>45.51143333333334</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>41.95912</v>
+        <v>70.37478</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>58.7006125</v>
+        <v>54.211675</v>
       </c>
       <c r="I30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>45.65322</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>57.63625</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>32.90455</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="P30" s="4" t="n">
+        <v>49.25876</v>
+      </c>
+      <c r="Q30" s="2" t="n">
         <v>22</v>
-      </c>
-      <c r="J30" s="4" t="n">
-        <v>18.10676</v>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="L30" s="4" t="n">
-        <v>66.55352500000001</v>
-      </c>
-      <c r="M30" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="N30" s="4" t="n">
-        <v>83.23505</v>
-      </c>
-      <c r="O30" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="P30" s="4" t="n">
-        <v>37.19218</v>
-      </c>
-      <c r="Q30" s="2" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>MRT</t>
+          <t>SLE</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Mauritania</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -5242,46 +5242,46 @@
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>45.51143333333334</v>
+        <v>47.22963333333333</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>68.15192</v>
+        <v>40.77244</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>54.211675</v>
+        <v>58.7006125</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>45.65322</v>
+        <v>18.10676</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>57.63625</v>
+        <v>66.55352500000001</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>32.90455</v>
+        <v>83.23505</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>48.85706</v>
+        <v>37.97442</v>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32">
@@ -5307,7 +5307,7 @@
         <v>34</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>49.10028</v>
+        <v>50.15578</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>37</v>
@@ -5337,10 +5337,10 @@
         <v>12</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>28.42378</v>
+        <v>29.07918</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33">
@@ -5366,10 +5366,10 @@
         <v>36</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>58.19593999999999</v>
+        <v>57.88006</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H33" s="4" t="n">
         <v>34.88317499999999</v>
@@ -5396,128 +5396,128 @@
         <v>3</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>38.26008</v>
+        <v>38.8309</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>LBR</t>
+          <t>BDI</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>47.28215</v>
+        <v>32.00036666666666</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>54.65236</v>
+        <v>48.15412</v>
       </c>
       <c r="G34" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>57.9424375</v>
+      </c>
+      <c r="I34" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="H34" s="4" t="n">
-        <v>44.7352125</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>44</v>
-      </c>
       <c r="J34" s="4" t="n">
-        <v>17.93482</v>
+        <v>28.81362</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>59.010625</v>
+        <v>50.357675</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>68.45417500000001</v>
+        <v>88.29044999999999</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>34.3624</v>
+        <v>25.4083</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>BDI</t>
+          <t>BFA</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>32.00036666666666</v>
+        <v>45.02548333333333</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>43.39212</v>
+        <v>56.07542000000001</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>57.9424375</v>
+        <v>52.87593750000001</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>28.81362</v>
+        <v>35.95978</v>
       </c>
       <c r="K35" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="L35" s="4" t="n">
+        <v>36.733</v>
+      </c>
+      <c r="M35" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="L35" s="4" t="n">
-        <v>50.357675</v>
-      </c>
-      <c r="M35" s="2" t="n">
-        <v>30</v>
-      </c>
       <c r="N35" s="4" t="n">
-        <v>88.29044999999999</v>
+        <v>64.17962499999999</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>23.61126</v>
+        <v>39.70784</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36">
@@ -5543,10 +5543,10 @@
         <v>38</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>56.95296</v>
+        <v>55.74172</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H36" s="4" t="n">
         <v>50.393225</v>
@@ -5573,7 +5573,7 @@
         <v>33</v>
       </c>
       <c r="P36" s="4" t="n">
-        <v>30.04626</v>
+        <v>30.7228</v>
       </c>
       <c r="Q36" s="2" t="n">
         <v>45</v>
@@ -5582,12 +5582,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>BFA</t>
+          <t>LBR</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -5596,234 +5596,234 @@
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>45.02548333333333</v>
+        <v>47.28215</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>50.36856</v>
+        <v>49.14776</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>52.87593750000001</v>
+        <v>44.7352125</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>35.95978</v>
+        <v>17.93482</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>36.733</v>
+        <v>59.010625</v>
       </c>
       <c r="M37" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="N37" s="4" t="n">
+        <v>68.45417500000001</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="P37" s="4" t="n">
+        <v>34.86980000000001</v>
+      </c>
+      <c r="Q37" s="2" t="n">
         <v>40</v>
-      </c>
-      <c r="N37" s="4" t="n">
-        <v>64.17962499999999</v>
-      </c>
-      <c r="O37" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="P37" s="4" t="n">
-        <v>37.1074</v>
-      </c>
-      <c r="Q37" s="2" t="n">
-        <v>38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>CMR</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>34.88985</v>
+        <v>38.8242</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>53.15652</v>
+        <v>50.80246</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>59.0416125</v>
+        <v>49.6033625</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>30.87028</v>
+        <v>29.20936</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>29.741975</v>
+        <v>31.66485</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>70.386825</v>
+        <v>80.06817500000001</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="P38" s="4" t="n">
-        <v>42.16096</v>
+        <v>41.16198</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>MOZ</t>
+          <t>CMR</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="D39" s="4" t="n">
-        <v>40.243</v>
+        <v>34.88985</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>46.29028</v>
+        <v>53.06912</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>49.2159125</v>
+        <v>59.0416125</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>26.58424</v>
+        <v>30.87028</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>40.631825</v>
+        <v>29.741975</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>82.998575</v>
+        <v>70.386825</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="P39" s="4" t="n">
-        <v>32.97534</v>
+        <v>42.16096</v>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>COG</t>
+          <t>LBY</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Republic of Congo</t>
+          <t>Libya</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>35.23868333333333</v>
+        <v>17.19116666666667</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>53.82208000000001</v>
+        <v>61.77938</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>50.75654285714285</v>
+        <v>68.133375</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>43.89399999999999</v>
+        <v>82.05138000000001</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>47.688075</v>
+        <v>34.8835</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>53.938425</v>
+        <v>1.6178</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="P40" s="4" t="n">
-        <v>33.16748</v>
+        <v>49.54613999999999</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>MOZ</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -5832,57 +5832,57 @@
         </is>
       </c>
       <c r="D41" s="4" t="n">
-        <v>38.8242</v>
+        <v>40.243</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>48.02668</v>
+        <v>41.9132</v>
       </c>
       <c r="G41" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>49.2159125</v>
+      </c>
+      <c r="I41" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="H41" s="4" t="n">
-        <v>49.6033625</v>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>38</v>
-      </c>
       <c r="J41" s="4" t="n">
-        <v>29.20936</v>
+        <v>26.58424</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>31.66485</v>
+        <v>40.631825</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>80.06817500000001</v>
+        <v>82.998575</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P41" s="4" t="n">
-        <v>40.90828</v>
+        <v>33.16562</v>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>AGO</t>
+          <t>COG</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>Republic of Congo</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -5891,164 +5891,164 @@
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>43.97308333333334</v>
+        <v>35.23868333333333</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>43.80356</v>
+        <v>48.08352</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>40.56135714285715</v>
+        <v>50.75654285714285</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>31.95518</v>
+        <v>43.89399999999999</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>41.9519</v>
+        <v>47.688075</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>72.421425</v>
+        <v>53.938425</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="P42" s="4" t="n">
-        <v>39.11682</v>
+        <v>33.52688000000001</v>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>LBY</t>
+          <t>MLI</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Libya</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D43" s="4" t="n">
-        <v>17.19116666666667</v>
+        <v>31.50275</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>61.21898000000001</v>
+        <v>59.23887999999999</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>68.133375</v>
+        <v>33.44275</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>82.05138000000001</v>
+        <v>38.5246</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>34.8835</v>
+        <v>34.186475</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>1.6178</v>
+        <v>69.79712499999999</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="P43" s="4" t="n">
-        <v>48.6582</v>
+        <v>46.18404</v>
       </c>
       <c r="Q43" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>MLI</t>
+          <t>AGO</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>31.50275</v>
+        <v>43.97308333333334</v>
       </c>
       <c r="E44" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>37.59006</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>40.56135714285715</v>
+      </c>
+      <c r="I44" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="F44" s="4" t="n">
-        <v>53.27908</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="H44" s="4" t="n">
-        <v>33.44275</v>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>50</v>
-      </c>
       <c r="J44" s="4" t="n">
-        <v>38.5246</v>
+        <v>31.95518</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>34.186475</v>
+        <v>41.9519</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>69.79712499999999</v>
+        <v>72.421425</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="P44" s="4" t="n">
-        <v>47.24112</v>
+        <v>40.04704</v>
       </c>
       <c r="Q44" s="2" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45">
@@ -6074,10 +6074,10 @@
         <v>43</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>31.9788</v>
+        <v>28.45318</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H45" s="4" t="n">
         <v>58.9952</v>
@@ -6107,7 +6107,7 @@
         <v>42.5044</v>
       </c>
       <c r="Q45" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46">
@@ -6133,7 +6133,7 @@
         <v>39</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>52.22548</v>
+        <v>50.62806</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>33</v>
@@ -6163,7 +6163,7 @@
         <v>20</v>
       </c>
       <c r="P46" s="4" t="n">
-        <v>44.70643999999999</v>
+        <v>44.98128</v>
       </c>
       <c r="Q46" s="2" t="n">
         <v>27</v>
@@ -6192,10 +6192,10 @@
         <v>31</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>59.96932</v>
+        <v>58.43803999999999</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H47" s="4" t="n">
         <v>33.075425</v>
@@ -6222,128 +6222,128 @@
         <v>45</v>
       </c>
       <c r="P47" s="4" t="n">
-        <v>33.17388</v>
+        <v>33.42758000000001</v>
       </c>
       <c r="Q47" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>GNQ</t>
+          <t>ERI</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Equatorial Guinea</t>
+          <t>Eritrea</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>29.38645</v>
+        <v>17.33791666666666</v>
       </c>
       <c r="E48" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>50.60994</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>38.693625</v>
+      </c>
+      <c r="I48" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="F48" s="4" t="n">
-        <v>70.98984</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H48" s="4" t="n">
-        <v>34.99632857142857</v>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>47</v>
-      </c>
       <c r="J48" s="4" t="n">
-        <v>23.7376</v>
+        <v>36.83042</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>32.965225</v>
+        <v>36.6521</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>37.108275</v>
+        <v>59.06247500000001</v>
       </c>
       <c r="O48" s="2" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="P48" s="4" t="n">
-        <v>34.9565</v>
+        <v>27.67012</v>
       </c>
       <c r="Q48" s="2" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>ERI</t>
+          <t>GNQ</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Eritrea</t>
+          <t>Equatorial Guinea</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="D49" s="4" t="n">
-        <v>17.33791666666666</v>
+        <v>29.38645</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>31.92326</v>
+        <v>51.55978</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>38.693625</v>
+        <v>34.99632857142857</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>36.83042</v>
+        <v>23.7376</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>36.6521</v>
+        <v>32.965225</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>59.06247500000001</v>
+        <v>37.108275</v>
       </c>
       <c r="O49" s="2" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="P49" s="4" t="n">
-        <v>27.47984</v>
+        <v>34.57594</v>
       </c>
       <c r="Q49" s="2" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50">
@@ -6369,10 +6369,10 @@
         <v>52</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>20.10936</v>
+        <v>20.4117</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H50" s="4" t="n">
         <v>50.0624875</v>
@@ -6402,7 +6402,7 @@
         <v>28.95128</v>
       </c>
       <c r="Q50" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51">
@@ -6428,10 +6428,10 @@
         <v>48</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>51.62694</v>
+        <v>52.76526</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H51" s="4" t="n">
         <v>34.92618571428572</v>
@@ -6458,7 +6458,7 @@
         <v>10</v>
       </c>
       <c r="P51" s="4" t="n">
-        <v>11.92028</v>
+        <v>12.00484</v>
       </c>
       <c r="Q51" s="2" t="n">
         <v>53</v>
@@ -6487,10 +6487,10 @@
         <v>47</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>51.2875</v>
+        <v>50.0255</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H52" s="4" t="n">
         <v>19.51824285714286</v>
@@ -6517,7 +6517,7 @@
         <v>34</v>
       </c>
       <c r="P52" s="4" t="n">
-        <v>17.90484</v>
+        <v>18.20084</v>
       </c>
       <c r="Q52" s="2" t="n">
         <v>51</v>
@@ -6526,119 +6526,119 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Central African Republic</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D53" s="4" t="n">
-        <v>21.01951666666666</v>
+        <v>11.12866666666667</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>46.71874</v>
+        <v>28.0149</v>
       </c>
       <c r="G53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>46.0569125</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="J53" s="4" t="n">
+        <v>14.64128</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="L53" s="4" t="n">
+        <v>12.6083</v>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="N53" s="4" t="n">
+        <v>51.69705</v>
+      </c>
+      <c r="O53" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="H53" s="4" t="n">
-        <v>21.491675</v>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="J53" s="4" t="n">
-        <v>9.56434</v>
-      </c>
-      <c r="K53" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="L53" s="4" t="n">
-        <v>10.3191</v>
-      </c>
-      <c r="M53" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="N53" s="4" t="n">
-        <v>75.682975</v>
-      </c>
-      <c r="O53" s="2" t="n">
-        <v>16</v>
-      </c>
       <c r="P53" s="4" t="n">
-        <v>13.94884</v>
+        <v>28.20786</v>
       </c>
       <c r="Q53" s="2" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Central African Republic</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>11.12866666666667</v>
+        <v>21.01951666666666</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>33.91284</v>
+        <v>38.45862</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>46.0569125</v>
+        <v>21.491675</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>14.64128</v>
+        <v>9.56434</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>12.6083</v>
+        <v>10.3191</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>51.69705</v>
+        <v>75.682975</v>
       </c>
       <c r="O54" s="2" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="P54" s="4" t="n">
-        <v>27.34106</v>
+        <v>14.0757</v>
       </c>
       <c r="Q54" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="55">
@@ -6664,10 +6664,10 @@
         <v>54</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>34.58764</v>
+        <v>16.58224</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H55" s="4" t="n">
         <v>11.82915</v>
@@ -15035,11 +15035,11 @@
       </c>
       <c r="D326" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E326" s="4" t="n">
-        <v>36.988</v>
+        <v>6.3087</v>
       </c>
     </row>
     <row r="327">
@@ -15060,11 +15060,11 @@
       </c>
       <c r="D327" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E327" s="4" t="n">
-        <v>43.7181</v>
+        <v>67.5784</v>
       </c>
     </row>
     <row r="328">
@@ -15085,11 +15085,11 @@
       </c>
       <c r="D328" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E328" s="4" t="n">
-        <v>44.652</v>
+        <v>29.5864</v>
       </c>
     </row>
     <row r="329">
@@ -15110,11 +15110,11 @@
       </c>
       <c r="D329" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E329" s="4" t="n">
-        <v>17.246</v>
+        <v>45.6744</v>
       </c>
     </row>
     <row r="330">
@@ -15135,11 +15135,11 @@
       </c>
       <c r="D330" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E330" s="4" t="n">
-        <v>36.6838</v>
+        <v>57.4644</v>
       </c>
     </row>
     <row r="331">
@@ -15160,11 +15160,11 @@
       </c>
       <c r="D331" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E331" s="4" t="n">
-        <v>59.2291</v>
+        <v>17.8767</v>
       </c>
     </row>
     <row r="332">
@@ -15185,11 +15185,11 @@
       </c>
       <c r="D332" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E332" s="4" t="n">
-        <v>47.8243</v>
+        <v>36.5596</v>
       </c>
     </row>
     <row r="333">
@@ -15210,11 +15210,11 @@
       </c>
       <c r="D333" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E333" s="4" t="n">
-        <v>20.5178</v>
+        <v>19.951</v>
       </c>
     </row>
     <row r="334">
@@ -15235,11 +15235,11 @@
       </c>
       <c r="D334" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E334" s="4" t="n">
-        <v>8.795299999999999</v>
+        <v>14.4233</v>
       </c>
     </row>
     <row r="335">
@@ -15260,11 +15260,11 @@
       </c>
       <c r="D335" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E335" s="4" t="n">
-        <v>48.0399</v>
+        <v>19.3577</v>
       </c>
     </row>
     <row r="336">
@@ -15285,11 +15285,11 @@
       </c>
       <c r="D336" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E336" s="4" t="n">
-        <v>15.4025</v>
+        <v>22.3717</v>
       </c>
     </row>
     <row r="337">
@@ -15310,11 +15310,11 @@
       </c>
       <c r="D337" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E337" s="4" t="n">
-        <v>53.5045</v>
+        <v>99.812</v>
       </c>
     </row>
     <row r="338">
@@ -15335,11 +15335,11 @@
       </c>
       <c r="D338" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E338" s="4" t="n">
-        <v>26.9156</v>
+        <v>37.7108</v>
       </c>
     </row>
     <row r="339">
@@ -15360,11 +15360,11 @@
       </c>
       <c r="D339" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E339" s="4" t="n">
-        <v>15.2601</v>
+        <v>29.6928</v>
       </c>
     </row>
     <row r="340">
@@ -15385,11 +15385,11 @@
       </c>
       <c r="D340" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E340" s="4" t="n">
-        <v>9.039300000000001</v>
+        <v>46.5138</v>
       </c>
     </row>
     <row r="341">
@@ -15410,11 +15410,11 @@
       </c>
       <c r="D341" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E341" s="4" t="n">
-        <v>3.6961</v>
+        <v>97.108</v>
       </c>
     </row>
     <row r="342">
@@ -15435,11 +15435,11 @@
       </c>
       <c r="D342" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E342" s="4" t="n">
-        <v>13.3064</v>
+        <v>27.0834</v>
       </c>
     </row>
     <row r="343">
@@ -15460,11 +15460,11 @@
       </c>
       <c r="D343" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E343" s="4" t="n">
-        <v>100</v>
+        <v>18.5426</v>
       </c>
     </row>
     <row r="344">
@@ -15485,11 +15485,11 @@
       </c>
       <c r="D344" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E344" s="4" t="n">
-        <v>23.3561</v>
+        <v>9.7683</v>
       </c>
     </row>
     <row r="345">
@@ -15510,11 +15510,11 @@
       </c>
       <c r="D345" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E345" s="4" t="n">
-        <v>14.9011</v>
+        <v>13.2025</v>
       </c>
     </row>
     <row r="346">
@@ -15535,11 +15535,11 @@
       </c>
       <c r="D346" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E346" s="4" t="n">
-        <v>37.177</v>
+        <v>10.7136</v>
       </c>
     </row>
     <row r="347">
@@ -15560,11 +15560,11 @@
       </c>
       <c r="D347" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E347" s="4" t="n">
-        <v>19.155</v>
+        <v>13.3178</v>
       </c>
     </row>
     <row r="348">
@@ -15585,11 +15585,11 @@
       </c>
       <c r="D348" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E348" s="4" t="n">
-        <v>100</v>
+        <v>3.6349</v>
       </c>
     </row>
     <row r="349">
@@ -15610,11 +15610,11 @@
       </c>
       <c r="D349" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E349" s="4" t="n">
-        <v>20.352</v>
+        <v>54.848</v>
       </c>
     </row>
     <row r="350">
@@ -15635,11 +15635,11 @@
       </c>
       <c r="D350" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E350" s="4" t="n">
-        <v>48.9187</v>
+        <v>21.3233</v>
       </c>
     </row>
     <row r="351">
@@ -15660,11 +15660,11 @@
       </c>
       <c r="D351" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E351" s="4" t="n">
-        <v>15.2601</v>
+        <v>17.8831</v>
       </c>
     </row>
     <row r="352">
@@ -15685,11 +15685,11 @@
       </c>
       <c r="D352" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E352" s="4" t="n">
-        <v>62.5209</v>
+        <v>40.0746</v>
       </c>
     </row>
     <row r="353">
@@ -15710,11 +15710,11 @@
       </c>
       <c r="D353" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E353" s="4" t="n">
-        <v>26.5767</v>
+        <v>100</v>
       </c>
     </row>
     <row r="354">
@@ -15735,11 +15735,11 @@
       </c>
       <c r="D354" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E354" s="4" t="n">
-        <v>19.4914</v>
+        <v>24.655</v>
       </c>
     </row>
     <row r="355">
@@ -15760,11 +15760,11 @@
       </c>
       <c r="D355" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E355" s="4" t="n">
-        <v>6.6405</v>
+        <v>36.3176</v>
       </c>
     </row>
     <row r="356">
@@ -15785,11 +15785,11 @@
       </c>
       <c r="D356" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E356" s="4" t="n">
-        <v>48.8416</v>
+        <v>26.8801</v>
       </c>
     </row>
     <row r="357">
@@ -15810,11 +15810,11 @@
       </c>
       <c r="D357" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E357" s="4" t="n">
-        <v>25.9938</v>
+        <v>36.9638</v>
       </c>
     </row>
     <row r="358">
@@ -15835,11 +15835,11 @@
       </c>
       <c r="D358" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E358" s="4" t="n">
-        <v>19.5734</v>
+        <v>100</v>
       </c>
     </row>
     <row r="359">
@@ -15860,11 +15860,11 @@
       </c>
       <c r="D359" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E359" s="4" t="n">
-        <v>43.7262</v>
+        <v>7.7699</v>
       </c>
     </row>
     <row r="360">
@@ -15885,11 +15885,11 @@
       </c>
       <c r="D360" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E360" s="4" t="n">
-        <v>42.8028</v>
+        <v>100</v>
       </c>
     </row>
     <row r="361">
@@ -15910,11 +15910,11 @@
       </c>
       <c r="D361" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E361" s="4" t="n">
-        <v>20.0295</v>
+        <v>12.4364</v>
       </c>
     </row>
     <row r="362">
@@ -15935,11 +15935,11 @@
       </c>
       <c r="D362" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E362" s="4" t="n">
-        <v>19.166</v>
+        <v>11.0244</v>
       </c>
     </row>
     <row r="363">
@@ -15960,11 +15960,11 @@
       </c>
       <c r="D363" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E363" s="4" t="n">
-        <v>15.1502</v>
+        <v>34.2052</v>
       </c>
     </row>
     <row r="364">
@@ -15985,11 +15985,11 @@
       </c>
       <c r="D364" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E364" s="4" t="n">
-        <v>1.8623</v>
+        <v>3.2951</v>
       </c>
     </row>
     <row r="365">
@@ -16010,11 +16010,11 @@
       </c>
       <c r="D365" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E365" s="4" t="n">
-        <v>23.7323</v>
+        <v>50.9337</v>
       </c>
     </row>
     <row r="366">
@@ -16035,11 +16035,11 @@
       </c>
       <c r="D366" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E366" s="4" t="n">
-        <v>6.039</v>
+        <v>0</v>
       </c>
     </row>
     <row r="367">
@@ -16060,11 +16060,11 @@
       </c>
       <c r="D367" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E367" s="4" t="n">
-        <v>32.4376</v>
+        <v>2.8836</v>
       </c>
     </row>
     <row r="368">
@@ -16085,11 +16085,11 @@
       </c>
       <c r="D368" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E368" s="4" t="n">
-        <v>93.5652</v>
+        <v>3.5382</v>
       </c>
     </row>
     <row r="369">
@@ -16110,11 +16110,11 @@
       </c>
       <c r="D369" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E369" s="4" t="n">
-        <v>15.4025</v>
+        <v>7.5846</v>
       </c>
     </row>
     <row r="370">
@@ -16135,11 +16135,11 @@
       </c>
       <c r="D370" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E370" s="4" t="n">
-        <v>13.6788</v>
+        <v>34.7952</v>
       </c>
     </row>
     <row r="371">
@@ -16160,11 +16160,11 @@
       </c>
       <c r="D371" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E371" s="4" t="n">
-        <v>7.1427</v>
+        <v>40.4976</v>
       </c>
     </row>
     <row r="372">
@@ -16185,11 +16185,11 @@
       </c>
       <c r="D372" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E372" s="4" t="n">
-        <v>15.2252</v>
+        <v>8.583</v>
       </c>
     </row>
     <row r="373">
@@ -16210,11 +16210,11 @@
       </c>
       <c r="D373" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E373" s="4" t="n">
-        <v>35.9948</v>
+        <v>42.1701</v>
       </c>
     </row>
     <row r="374">
@@ -16235,11 +16235,11 @@
       </c>
       <c r="D374" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E374" s="4" t="n">
-        <v>23.5619</v>
+        <v>100</v>
       </c>
     </row>
     <row r="375">
@@ -16260,11 +16260,11 @@
       </c>
       <c r="D375" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E375" s="4" t="n">
-        <v>13.4155</v>
+        <v>25.0375</v>
       </c>
     </row>
     <row r="376">
@@ -16285,11 +16285,11 @@
       </c>
       <c r="D376" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E376" s="4" t="n">
-        <v>21.6964</v>
+        <v>20.363</v>
       </c>
     </row>
     <row r="377">
@@ -16310,11 +16310,11 @@
       </c>
       <c r="D377" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E377" s="4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="378">
@@ -16335,11 +16335,11 @@
       </c>
       <c r="D378" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E378" s="4" t="n">
-        <v>54.6191</v>
+        <v>25.6984</v>
       </c>
     </row>
     <row r="379">
@@ -16360,11 +16360,11 @@
       </c>
       <c r="D379" s="3" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="E379" s="4" t="n">
-        <v>22.6865</v>
+        <v>4.9465</v>
       </c>
     </row>
     <row r="380">
@@ -17739,7 +17739,7 @@
         </is>
       </c>
       <c r="E434" s="4" t="n">
-        <v>70.4152</v>
+        <v>70.027</v>
       </c>
     </row>
     <row r="435">
@@ -17764,7 +17764,7 @@
         </is>
       </c>
       <c r="E435" s="4" t="n">
-        <v>1.1058</v>
+        <v>1.0555</v>
       </c>
     </row>
     <row r="436">
@@ -17789,7 +17789,7 @@
         </is>
       </c>
       <c r="E436" s="4" t="n">
-        <v>43.6454</v>
+        <v>43.7631</v>
       </c>
     </row>
     <row r="437">
@@ -17814,7 +17814,7 @@
         </is>
       </c>
       <c r="E437" s="4" t="n">
-        <v>29.8189</v>
+        <v>29.9248</v>
       </c>
     </row>
     <row r="438">
@@ -17839,7 +17839,7 @@
         </is>
       </c>
       <c r="E438" s="4" t="n">
-        <v>93.3888</v>
+        <v>93.6571</v>
       </c>
     </row>
     <row r="439">
@@ -17864,7 +17864,7 @@
         </is>
       </c>
       <c r="E439" s="4" t="n">
-        <v>2.9046</v>
+        <v>2.9564</v>
       </c>
     </row>
     <row r="440">
@@ -17889,7 +17889,7 @@
         </is>
       </c>
       <c r="E440" s="4" t="n">
-        <v>61.4209</v>
+        <v>61.5672</v>
       </c>
     </row>
     <row r="441">
@@ -17914,7 +17914,7 @@
         </is>
       </c>
       <c r="E441" s="4" t="n">
-        <v>51.153</v>
+        <v>51.2828</v>
       </c>
     </row>
     <row r="442">
@@ -17939,7 +17939,7 @@
         </is>
       </c>
       <c r="E442" s="4" t="n">
-        <v>14.7702</v>
+        <v>14.8338</v>
       </c>
     </row>
     <row r="443">
@@ -17964,7 +17964,7 @@
         </is>
       </c>
       <c r="E443" s="4" t="n">
-        <v>58.5799</v>
+        <v>58.5693</v>
       </c>
     </row>
     <row r="444">
@@ -17989,7 +17989,7 @@
         </is>
       </c>
       <c r="E444" s="4" t="n">
-        <v>39.9608</v>
+        <v>40.7513</v>
       </c>
     </row>
     <row r="445">
@@ -18014,7 +18014,7 @@
         </is>
       </c>
       <c r="E445" s="4" t="n">
-        <v>73.6961</v>
+        <v>73.78489999999999</v>
       </c>
     </row>
     <row r="446">
@@ -18039,7 +18039,7 @@
         </is>
       </c>
       <c r="E446" s="4" t="n">
-        <v>62.0123</v>
+        <v>62.1596</v>
       </c>
     </row>
     <row r="447">
@@ -18064,7 +18064,7 @@
         </is>
       </c>
       <c r="E447" s="4" t="n">
-        <v>88.41670000000001</v>
+        <v>88.6067</v>
       </c>
     </row>
     <row r="448">
@@ -18089,7 +18089,7 @@
         </is>
       </c>
       <c r="E448" s="4" t="n">
-        <v>91.02290000000001</v>
+        <v>91.2171</v>
       </c>
     </row>
     <row r="449">
@@ -18114,7 +18114,7 @@
         </is>
       </c>
       <c r="E449" s="4" t="n">
-        <v>13.3367</v>
+        <v>13.3582</v>
       </c>
     </row>
     <row r="450">
@@ -18139,7 +18139,7 @@
         </is>
       </c>
       <c r="E450" s="4" t="n">
-        <v>33.9344</v>
+        <v>34.0363</v>
       </c>
     </row>
     <row r="451">
@@ -18164,7 +18164,7 @@
         </is>
       </c>
       <c r="E451" s="4" t="n">
-        <v>94.8896</v>
+        <v>95.09</v>
       </c>
     </row>
     <row r="452">
@@ -18189,7 +18189,7 @@
         </is>
       </c>
       <c r="E452" s="4" t="n">
-        <v>62.8722</v>
+        <v>63.0999</v>
       </c>
     </row>
     <row r="453">
@@ -18214,7 +18214,7 @@
         </is>
       </c>
       <c r="E453" s="4" t="n">
-        <v>44.5882</v>
+        <v>44.7074</v>
       </c>
     </row>
     <row r="454">
@@ -18239,7 +18239,7 @@
         </is>
       </c>
       <c r="E454" s="4" t="n">
-        <v>35.7394</v>
+        <v>35.8443</v>
       </c>
     </row>
     <row r="455">
@@ -18264,7 +18264,7 @@
         </is>
       </c>
       <c r="E455" s="4" t="n">
-        <v>32.2308</v>
+        <v>32.0118</v>
       </c>
     </row>
     <row r="456">
@@ -18289,7 +18289,7 @@
         </is>
       </c>
       <c r="E456" s="4" t="n">
-        <v>88.3172</v>
+        <v>87.532</v>
       </c>
     </row>
     <row r="457">
@@ -18314,7 +18314,7 @@
         </is>
       </c>
       <c r="E457" s="4" t="n">
-        <v>56.7648</v>
+        <v>56.8836</v>
       </c>
     </row>
     <row r="458">
@@ -18339,7 +18339,7 @@
         </is>
       </c>
       <c r="E458" s="4" t="n">
-        <v>15.6487</v>
+        <v>15.7211</v>
       </c>
     </row>
     <row r="459">
@@ -18364,7 +18364,7 @@
         </is>
       </c>
       <c r="E459" s="4" t="n">
-        <v>81.6486</v>
+        <v>81.8276</v>
       </c>
     </row>
     <row r="460">
@@ -18389,7 +18389,7 @@
         </is>
       </c>
       <c r="E460" s="4" t="n">
-        <v>30.9774</v>
+        <v>31.7728</v>
       </c>
     </row>
     <row r="461">
@@ -18414,7 +18414,7 @@
         </is>
       </c>
       <c r="E461" s="4" t="n">
-        <v>71.35250000000001</v>
+        <v>71.5149</v>
       </c>
     </row>
     <row r="462">
@@ -18439,7 +18439,7 @@
         </is>
       </c>
       <c r="E462" s="4" t="n">
-        <v>15.8646</v>
+        <v>15.9785</v>
       </c>
     </row>
     <row r="463">
@@ -18464,7 +18464,7 @@
         </is>
       </c>
       <c r="E463" s="4" t="n">
-        <v>34.2021</v>
+        <v>34.324</v>
       </c>
     </row>
     <row r="464">
@@ -18489,7 +18489,7 @@
         </is>
       </c>
       <c r="E464" s="4" t="n">
-        <v>12.6415</v>
+        <v>12.7176</v>
       </c>
     </row>
     <row r="465">
@@ -18514,7 +18514,7 @@
         </is>
       </c>
       <c r="E465" s="4" t="n">
-        <v>60.1239</v>
+        <v>60.2682</v>
       </c>
     </row>
     <row r="466">
@@ -18564,7 +18564,7 @@
         </is>
       </c>
       <c r="E467" s="4" t="n">
-        <v>15.4151</v>
+        <v>15.4872</v>
       </c>
     </row>
     <row r="468">
@@ -18589,7 +18589,7 @@
         </is>
       </c>
       <c r="E468" s="4" t="n">
-        <v>75.09050000000001</v>
+        <v>75.2432</v>
       </c>
     </row>
     <row r="469">
@@ -18614,7 +18614,7 @@
         </is>
       </c>
       <c r="E469" s="4" t="n">
-        <v>18.6107</v>
+        <v>18.5474</v>
       </c>
     </row>
     <row r="470">
@@ -18639,7 +18639,7 @@
         </is>
       </c>
       <c r="E470" s="4" t="n">
-        <v>66.9251</v>
+        <v>67.0796</v>
       </c>
     </row>
     <row r="471">
@@ -18664,7 +18664,7 @@
         </is>
       </c>
       <c r="E471" s="4" t="n">
-        <v>37.8644</v>
+        <v>38.5682</v>
       </c>
     </row>
     <row r="472">
@@ -18689,7 +18689,7 @@
         </is>
       </c>
       <c r="E472" s="4" t="n">
-        <v>19.6369</v>
+        <v>19.7158</v>
       </c>
     </row>
     <row r="473">
@@ -18714,7 +18714,7 @@
         </is>
       </c>
       <c r="E473" s="4" t="n">
-        <v>47.9948</v>
+        <v>48.2423</v>
       </c>
     </row>
     <row r="474">
@@ -18739,7 +18739,7 @@
         </is>
       </c>
       <c r="E474" s="4" t="n">
-        <v>36.1724</v>
+        <v>36.278</v>
       </c>
     </row>
     <row r="475">
@@ -18764,7 +18764,7 @@
         </is>
       </c>
       <c r="E475" s="4" t="n">
-        <v>10.6124</v>
+        <v>10.6767</v>
       </c>
     </row>
     <row r="476">
@@ -18814,7 +18814,7 @@
         </is>
       </c>
       <c r="E477" s="4" t="n">
-        <v>54.7381</v>
+        <v>54.9952</v>
       </c>
     </row>
     <row r="478">
@@ -18839,7 +18839,7 @@
         </is>
       </c>
       <c r="E478" s="4" t="n">
-        <v>75.4016</v>
+        <v>75.58880000000001</v>
       </c>
     </row>
     <row r="479">
@@ -18889,7 +18889,7 @@
         </is>
       </c>
       <c r="E480" s="4" t="n">
-        <v>28.0551</v>
+        <v>28.3873</v>
       </c>
     </row>
     <row r="481">
@@ -18914,7 +18914,7 @@
         </is>
       </c>
       <c r="E481" s="4" t="n">
-        <v>34.6945</v>
+        <v>38.8236</v>
       </c>
     </row>
     <row r="482">
@@ -18939,7 +18939,7 @@
         </is>
       </c>
       <c r="E482" s="4" t="n">
-        <v>82.1377</v>
+        <v>82.3175</v>
       </c>
     </row>
     <row r="483">
@@ -18964,7 +18964,7 @@
         </is>
       </c>
       <c r="E483" s="4" t="n">
-        <v>42.0423</v>
+        <v>42.1574</v>
       </c>
     </row>
     <row r="484">
@@ -18989,7 +18989,7 @@
         </is>
       </c>
       <c r="E484" s="4" t="n">
-        <v>33.7933</v>
+        <v>33.895</v>
       </c>
     </row>
     <row r="485">
@@ -19014,7 +19014,7 @@
         </is>
       </c>
       <c r="E485" s="4" t="n">
-        <v>84.1632</v>
+        <v>84.3463</v>
       </c>
     </row>
     <row r="486">
@@ -19039,7 +19039,7 @@
         </is>
       </c>
       <c r="E486" s="4" t="n">
-        <v>41.9969</v>
+        <v>42.1119</v>
       </c>
     </row>
     <row r="487">
@@ -19064,7 +19064,7 @@
         </is>
       </c>
       <c r="E487" s="4" t="n">
-        <v>53.0644</v>
+        <v>53.1763</v>
       </c>
     </row>
     <row r="488">
@@ -46049,7 +46049,7 @@
         </is>
       </c>
       <c r="E1568" s="4" t="n">
-        <v>48.3087</v>
+        <v>52.9598</v>
       </c>
     </row>
     <row r="1569">
@@ -46074,7 +46074,7 @@
         </is>
       </c>
       <c r="E1569" s="4" t="n">
-        <v>6.5539</v>
+        <v>15.5391</v>
       </c>
     </row>
     <row r="1570">
@@ -46099,7 +46099,7 @@
         </is>
       </c>
       <c r="E1570" s="4" t="n">
-        <v>54.5455</v>
+        <v>56.6596</v>
       </c>
     </row>
     <row r="1571">
@@ -46124,7 +46124,7 @@
         </is>
       </c>
       <c r="E1571" s="4" t="n">
-        <v>17.2304</v>
+        <v>30.2326</v>
       </c>
     </row>
     <row r="1572">
@@ -46149,7 +46149,7 @@
         </is>
       </c>
       <c r="E1572" s="4" t="n">
-        <v>74.63</v>
+        <v>79.0698</v>
       </c>
     </row>
     <row r="1573">
@@ -46174,7 +46174,7 @@
         </is>
       </c>
       <c r="E1573" s="4" t="n">
-        <v>12.8964</v>
+        <v>13.5307</v>
       </c>
     </row>
     <row r="1574">
@@ -46199,7 +46199,7 @@
         </is>
       </c>
       <c r="E1574" s="4" t="n">
-        <v>70.8245</v>
+        <v>71.3531</v>
       </c>
     </row>
     <row r="1575">
@@ -46249,7 +46249,7 @@
         </is>
       </c>
       <c r="E1576" s="4" t="n">
-        <v>17.6533</v>
+        <v>18.0761</v>
       </c>
     </row>
     <row r="1577">
@@ -46274,7 +46274,7 @@
         </is>
       </c>
       <c r="E1577" s="4" t="n">
-        <v>48.5201</v>
+        <v>50.3171</v>
       </c>
     </row>
     <row r="1578">
@@ -46299,7 +46299,7 @@
         </is>
       </c>
       <c r="E1578" s="4" t="n">
-        <v>89.2178</v>
+        <v>91.22620000000001</v>
       </c>
     </row>
     <row r="1579">
@@ -46324,7 +46324,7 @@
         </is>
       </c>
       <c r="E1579" s="4" t="n">
-        <v>98.5201</v>
+        <v>98.3087</v>
       </c>
     </row>
     <row r="1580">
@@ -46349,7 +46349,7 @@
         </is>
       </c>
       <c r="E1580" s="4" t="n">
-        <v>63.2135</v>
+        <v>67.4419</v>
       </c>
     </row>
     <row r="1581">
@@ -46424,7 +46424,7 @@
         </is>
       </c>
       <c r="E1583" s="4" t="n">
-        <v>51.797</v>
+        <v>52.7484</v>
       </c>
     </row>
     <row r="1584">
@@ -46449,7 +46449,7 @@
         </is>
       </c>
       <c r="E1584" s="4" t="n">
-        <v>52.8541</v>
+        <v>54.1226</v>
       </c>
     </row>
     <row r="1585">
@@ -46474,7 +46474,7 @@
         </is>
       </c>
       <c r="E1585" s="4" t="n">
-        <v>93.7632</v>
+        <v>94.8203</v>
       </c>
     </row>
     <row r="1586">
@@ -46499,7 +46499,7 @@
         </is>
       </c>
       <c r="E1586" s="4" t="n">
-        <v>88.9006</v>
+        <v>91.4376</v>
       </c>
     </row>
     <row r="1587">
@@ -46524,7 +46524,7 @@
         </is>
       </c>
       <c r="E1587" s="4" t="n">
-        <v>48.3087</v>
+        <v>51.1628</v>
       </c>
     </row>
     <row r="1588">
@@ -46549,7 +46549,7 @@
         </is>
       </c>
       <c r="E1588" s="4" t="n">
-        <v>65.0106</v>
+        <v>67.2304</v>
       </c>
     </row>
     <row r="1589">
@@ -46574,7 +46574,7 @@
         </is>
       </c>
       <c r="E1589" s="4" t="n">
-        <v>37.1036</v>
+        <v>40.4863</v>
       </c>
     </row>
     <row r="1590">
@@ -46599,7 +46599,7 @@
         </is>
       </c>
       <c r="E1590" s="4" t="n">
-        <v>65.0106</v>
+        <v>63.1078</v>
       </c>
     </row>
     <row r="1591">
@@ -46624,7 +46624,7 @@
         </is>
       </c>
       <c r="E1591" s="4" t="n">
-        <v>74.84139999999999</v>
+        <v>75.6871</v>
       </c>
     </row>
     <row r="1592">
@@ -46649,7 +46649,7 @@
         </is>
       </c>
       <c r="E1592" s="4" t="n">
-        <v>28.6469</v>
+        <v>31.1839</v>
       </c>
     </row>
     <row r="1593">
@@ -46674,7 +46674,7 @@
         </is>
       </c>
       <c r="E1593" s="4" t="n">
-        <v>71.67019999999999</v>
+        <v>76.1099</v>
       </c>
     </row>
     <row r="1594">
@@ -46699,7 +46699,7 @@
         </is>
       </c>
       <c r="E1594" s="4" t="n">
-        <v>54.8626</v>
+        <v>58.351</v>
       </c>
     </row>
     <row r="1595">
@@ -46749,7 +46749,7 @@
         </is>
       </c>
       <c r="E1596" s="4" t="n">
-        <v>35.9408</v>
+        <v>39.2178</v>
       </c>
     </row>
     <row r="1597">
@@ -46774,7 +46774,7 @@
         </is>
       </c>
       <c r="E1597" s="4" t="n">
-        <v>51.9027</v>
+        <v>46.6173</v>
       </c>
     </row>
     <row r="1598">
@@ -46799,7 +46799,7 @@
         </is>
       </c>
       <c r="E1598" s="4" t="n">
-        <v>32.3467</v>
+        <v>33.2981</v>
       </c>
     </row>
     <row r="1599">
@@ -46824,7 +46824,7 @@
         </is>
       </c>
       <c r="E1599" s="4" t="n">
-        <v>47.463</v>
+        <v>49.4715</v>
       </c>
     </row>
     <row r="1600">
@@ -46899,7 +46899,7 @@
         </is>
       </c>
       <c r="E1602" s="4" t="n">
-        <v>54.2283</v>
+        <v>56.9767</v>
       </c>
     </row>
     <row r="1603">
@@ -46924,7 +46924,7 @@
         </is>
       </c>
       <c r="E1603" s="4" t="n">
-        <v>15.5391</v>
+        <v>16.8076</v>
       </c>
     </row>
     <row r="1604">
@@ -46949,7 +46949,7 @@
         </is>
       </c>
       <c r="E1604" s="4" t="n">
-        <v>58.9852</v>
+        <v>60.3594</v>
       </c>
     </row>
     <row r="1605">
@@ -46974,7 +46974,7 @@
         </is>
       </c>
       <c r="E1605" s="4" t="n">
-        <v>61.8393</v>
+        <v>70.40170000000001</v>
       </c>
     </row>
     <row r="1606">
@@ -47024,7 +47024,7 @@
         </is>
       </c>
       <c r="E1607" s="4" t="n">
-        <v>72.7273</v>
+        <v>81.9239</v>
       </c>
     </row>
     <row r="1608">
@@ -47049,7 +47049,7 @@
         </is>
       </c>
       <c r="E1608" s="4" t="n">
-        <v>31.8182</v>
+        <v>35.7294</v>
       </c>
     </row>
     <row r="1609">
@@ -47074,7 +47074,7 @@
         </is>
       </c>
       <c r="E1609" s="4" t="n">
-        <v>47.463</v>
+        <v>51.797</v>
       </c>
     </row>
     <row r="1610">
@@ -47124,7 +47124,7 @@
         </is>
       </c>
       <c r="E1611" s="4" t="n">
-        <v>80.23260000000001</v>
+        <v>76.4271</v>
       </c>
     </row>
     <row r="1612">
@@ -47149,7 +47149,7 @@
         </is>
       </c>
       <c r="E1612" s="4" t="n">
-        <v>85.6237</v>
+        <v>88.6892</v>
       </c>
     </row>
     <row r="1613">
@@ -47199,7 +47199,7 @@
         </is>
       </c>
       <c r="E1614" s="4" t="n">
-        <v>6.9767</v>
+        <v>8.4567</v>
       </c>
     </row>
     <row r="1615">
@@ -47224,7 +47224,7 @@
         </is>
       </c>
       <c r="E1615" s="4" t="n">
-        <v>56.871</v>
+        <v>58.8795</v>
       </c>
     </row>
     <row r="1616">
@@ -47274,7 +47274,7 @@
         </is>
       </c>
       <c r="E1617" s="4" t="n">
-        <v>45.3488</v>
+        <v>49.6829</v>
       </c>
     </row>
     <row r="1618">
@@ -47299,7 +47299,7 @@
         </is>
       </c>
       <c r="E1618" s="4" t="n">
-        <v>48.7315</v>
+        <v>52.7484</v>
       </c>
     </row>
     <row r="1619">
@@ -47324,7 +47324,7 @@
         </is>
       </c>
       <c r="E1619" s="4" t="n">
-        <v>86.9979</v>
+        <v>89.64060000000001</v>
       </c>
     </row>
     <row r="1620">
@@ -47349,7 +47349,7 @@
         </is>
       </c>
       <c r="E1620" s="4" t="n">
-        <v>48.3087</v>
+        <v>50.9514</v>
       </c>
     </row>
     <row r="1621">
@@ -50171,7 +50171,7 @@
         <v>0.1429</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.1709</v>
+        <v>0.1642</v>
       </c>
       <c r="E2" s="6" t="n">
         <v>0.05</v>
@@ -50180,7 +50180,7 @@
         <v>0.25</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.1789</v>
+        <v>0.1752</v>
       </c>
       <c r="H2" s="6" t="n">
         <v>0.1429</v>
@@ -50201,7 +50201,7 @@
         <v>0.1429</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.1216</v>
+        <v>0.1531</v>
       </c>
       <c r="E3" s="6" t="n">
         <v>0.05</v>
@@ -50210,7 +50210,7 @@
         <v>0.25</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.0475</v>
+        <v>0.0704</v>
       </c>
       <c r="H3" s="6" t="n">
         <v>0.1429</v>
@@ -50231,7 +50231,7 @@
         <v>0.1429</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.1836</v>
+        <v>0.1771</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>0.05</v>
@@ -50240,7 +50240,7 @@
         <v>0.25</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0794</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>0.1429</v>
@@ -50261,7 +50261,7 @@
         <v>0.1429</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.1714</v>
+        <v>0.1675</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>0.05</v>
@@ -50270,7 +50270,7 @@
         <v>0.25</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.2164</v>
+        <v>0.2119</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>0.1429</v>
@@ -50291,7 +50291,7 @@
         <v>0.1429</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.1608</v>
+        <v>0.1529</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>0.05</v>
@@ -50300,7 +50300,7 @@
         <v>0.25</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.1409</v>
+        <v>0.138</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>0.1429</v>
@@ -50330,7 +50330,7 @@
         <v>0.25</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.1678</v>
+        <v>0.1643</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>0.1429</v>
@@ -50351,7 +50351,7 @@
         <v>0.1429</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.1916</v>
+        <v>0.1852</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>0.05</v>
@@ -50360,7 +50360,7 @@
         <v>0.25</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.1674</v>
+        <v>0.1609</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>0.1429</v>
